--- a/downloads/Th2_pre_post_results.xlsx
+++ b/downloads/Th2_pre_post_results.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C4">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C7">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C10">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C13">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C16">

--- a/downloads/Th2_pre_post_results.xlsx
+++ b/downloads/Th2_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -997,39 +997,39 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.3776102258227689</v>
+        <v>0.343790229917624</v>
       </c>
       <c r="E5">
-        <v>0.08333859038200342</v>
+        <v>0.03531559579533111</v>
       </c>
       <c r="F5">
-        <v>0.6718818612635343</v>
+        <v>0.6522648640399169</v>
       </c>
       <c r="G5">
-        <v>0.01513018806157836</v>
+        <v>0.03128788931776465</v>
       </c>
       <c r="H5">
-        <v>0.2659564684163583</v>
+        <v>0.2643268093716257</v>
       </c>
       <c r="I5">
-        <v>0.6509838058961923</v>
+        <v>0.593648173630563</v>
       </c>
       <c r="J5">
-        <v>-0.7591023186579464</v>
+        <v>-0.8005112838665484</v>
       </c>
       <c r="K5">
-        <v>1.514322770303484</v>
+        <v>1.488091743701796</v>
       </c>
     </row>
     <row r="6">
@@ -1038,35 +1038,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0.3899521832239537</v>
+        <v>0.3776102258227689</v>
       </c>
       <c r="E6">
-        <v>0.08985415048620604</v>
+        <v>0.08333859038200342</v>
       </c>
       <c r="F6">
-        <v>0.6900502159617014</v>
+        <v>0.6718818612635343</v>
       </c>
       <c r="G6">
-        <v>0.01409895110519824</v>
+        <v>0.01513018806157836</v>
       </c>
       <c r="H6">
-        <v>0.2189579073583054</v>
+        <v>0.2659564684163583</v>
       </c>
       <c r="I6">
-        <v>0.6446825948707755</v>
+        <v>0.6509838058961923</v>
       </c>
       <c r="J6">
-        <v>-0.6466182688963804</v>
+        <v>-0.7591023186579464</v>
       </c>
       <c r="K6">
-        <v>1.426522635344288</v>
+        <v>1.514322770303484</v>
       </c>
     </row>
     <row r="7">
@@ -1075,109 +1075,109 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>0.4279270937444796</v>
+        <v>0.3899521832239537</v>
       </c>
       <c r="E7">
-        <v>0.06881446305786842</v>
+        <v>0.08985415048620604</v>
       </c>
       <c r="F7">
-        <v>0.7870397244310907</v>
+        <v>0.6900502159617014</v>
       </c>
       <c r="G7">
-        <v>0.02310279689067599</v>
+        <v>0.01409895110519824</v>
       </c>
       <c r="H7">
-        <v>0.3337424351980456</v>
+        <v>0.2189579073583054</v>
       </c>
       <c r="I7">
-        <v>0.7084478211257073</v>
+        <v>0.6446825948707755</v>
       </c>
       <c r="J7">
-        <v>-0.8761761836224681</v>
+        <v>-0.6466182688963804</v>
       </c>
       <c r="K7">
-        <v>1.732030371111427</v>
+        <v>1.426522635344288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>0.3791406439477507</v>
+        <v>0.4279270937444796</v>
       </c>
       <c r="E8">
-        <v>0.08649860202376497</v>
+        <v>0.06881446305786842</v>
       </c>
       <c r="F8">
-        <v>0.6717826858717364</v>
+        <v>0.7870397244310907</v>
       </c>
       <c r="G8">
-        <v>0.01433674985839689</v>
+        <v>0.02310279689067599</v>
       </c>
       <c r="H8">
-        <v>0.2749194191854241</v>
+        <v>0.3337424351980456</v>
       </c>
       <c r="I8">
-        <v>0.7021964722010504</v>
+        <v>0.7084478211257073</v>
       </c>
       <c r="J8">
-        <v>-0.7743036674037778</v>
+        <v>-0.8761761836224681</v>
       </c>
       <c r="K8">
-        <v>1.532584955299279</v>
+        <v>1.732030371111427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>0.3913024394546835</v>
+        <v>0.3464173336442669</v>
       </c>
       <c r="E9">
-        <v>0.09298722925741842</v>
+        <v>0.03867607389820921</v>
       </c>
       <c r="F9">
-        <v>0.6896176496519486</v>
+        <v>0.6541585933903244</v>
       </c>
       <c r="G9">
-        <v>0.01336267741347996</v>
+        <v>0.02986434555579367</v>
       </c>
       <c r="H9">
-        <v>0.2357571137579758</v>
+        <v>0.2751110935395687</v>
       </c>
       <c r="I9">
-        <v>0.6967380423702259</v>
+        <v>0.6451634606922368</v>
       </c>
       <c r="J9">
-        <v>-0.6809240551017621</v>
+        <v>-0.8184239461891358</v>
       </c>
       <c r="K9">
-        <v>1.463528934011129</v>
+        <v>1.51125861347767</v>
       </c>
     </row>
     <row r="10">
@@ -1186,151 +1186,151 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>0.4297566568787797</v>
+        <v>0.3791406439477507</v>
       </c>
       <c r="E10">
-        <v>0.07289617252985897</v>
+        <v>0.08649860202376497</v>
       </c>
       <c r="F10">
-        <v>0.7866171412277005</v>
+        <v>0.6717826858717364</v>
       </c>
       <c r="G10">
-        <v>0.02193641133818026</v>
+        <v>0.01433674985839689</v>
       </c>
       <c r="H10">
-        <v>0.340143496257349</v>
+        <v>0.2749194191854241</v>
       </c>
       <c r="I10">
-        <v>0.7511256611508594</v>
+        <v>0.7021964722010504</v>
       </c>
       <c r="J10">
-        <v>-0.8845833391388808</v>
+        <v>-0.7743036674037778</v>
       </c>
       <c r="K10">
-        <v>1.74409665289644</v>
+        <v>1.532584955299279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C11">
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0.3795726879861507</v>
+        <v>0.3913024394546835</v>
       </c>
       <c r="E11">
-        <v>0.08975489200164144</v>
+        <v>0.09298722925741842</v>
       </c>
       <c r="F11">
-        <v>0.66939048397066</v>
+        <v>0.6896176496519486</v>
       </c>
       <c r="G11">
-        <v>0.01348070052804915</v>
+        <v>0.01336267741347996</v>
       </c>
       <c r="H11">
-        <v>0.2810366516316445</v>
+        <v>0.2357571137579758</v>
       </c>
       <c r="I11">
-        <v>0.7537977604818319</v>
+        <v>0.6967380423702259</v>
       </c>
       <c r="J11">
-        <v>-0.7845370187976408</v>
+        <v>-0.6809240551017621</v>
       </c>
       <c r="K11">
-        <v>1.543682394769942</v>
+        <v>1.463528934011129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>0.3910464225211037</v>
+        <v>0.4297566568787797</v>
       </c>
       <c r="E12">
-        <v>0.09596359841164659</v>
+        <v>0.07289617252985897</v>
       </c>
       <c r="F12">
-        <v>0.6861292466305609</v>
+        <v>0.7866171412277005</v>
       </c>
       <c r="G12">
-        <v>0.01259682863688801</v>
+        <v>0.02193641133818026</v>
       </c>
       <c r="H12">
-        <v>0.2497103853753709</v>
+        <v>0.340143496257349</v>
       </c>
       <c r="I12">
-        <v>0.7491935493890896</v>
+        <v>0.7511256611508594</v>
       </c>
       <c r="J12">
-        <v>-0.7094381204235447</v>
+        <v>-0.8845833391388808</v>
       </c>
       <c r="K12">
-        <v>1.491530965465752</v>
+        <v>1.74409665289644</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>0.4302601096673905</v>
+        <v>0.3485159356200326</v>
       </c>
       <c r="E13">
-        <v>0.07712537718144957</v>
+        <v>0.04236451832976129</v>
       </c>
       <c r="F13">
-        <v>0.7833948421533314</v>
+        <v>0.654667352910304</v>
       </c>
       <c r="G13">
-        <v>0.02070076115083226</v>
+        <v>0.02832331881242682</v>
       </c>
       <c r="H13">
-        <v>0.3432080428674738</v>
+        <v>0.283857927592792</v>
       </c>
       <c r="I13">
-        <v>0.7941338554367682</v>
+        <v>0.6969421191342569</v>
       </c>
       <c r="J13">
-        <v>-0.8878993306723153</v>
+        <v>-0.832322531822119</v>
       </c>
       <c r="K13">
-        <v>1.748419550007096</v>
+        <v>1.529354403062184</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>0.3778803831558597</v>
+        <v>0.3795726879861507</v>
       </c>
       <c r="E14">
-        <v>0.0927722121850526</v>
+        <v>0.08975489200164144</v>
       </c>
       <c r="F14">
-        <v>0.6629885541266668</v>
+        <v>0.66939048397066</v>
       </c>
       <c r="G14">
-        <v>0.01258669033108263</v>
+        <v>0.01348070052804915</v>
       </c>
       <c r="H14">
-        <v>0.2827788554998992</v>
+        <v>0.2810366516316445</v>
       </c>
       <c r="I14">
-        <v>0.8060757025672275</v>
+        <v>0.7537977604818319</v>
       </c>
       <c r="J14">
-        <v>-0.7878796200183311</v>
+        <v>-0.7845370187976408</v>
       </c>
       <c r="K14">
-        <v>1.543640386330051</v>
+        <v>1.543682394769942</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1378,33 +1378,33 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.3880491126151497</v>
+        <v>0.3910464225211037</v>
       </c>
       <c r="E15">
-        <v>0.09835464888198936</v>
+        <v>0.09596359841164659</v>
       </c>
       <c r="F15">
-        <v>0.67774357634831</v>
+        <v>0.6861292466305609</v>
       </c>
       <c r="G15">
-        <v>0.01183191274568021</v>
+        <v>0.01259682863688801</v>
       </c>
       <c r="H15">
-        <v>0.2592882396367674</v>
+        <v>0.2497103853753709</v>
       </c>
       <c r="I15">
-        <v>0.8023464237891476</v>
+        <v>0.7491935493890896</v>
       </c>
       <c r="J15">
-        <v>-0.730600062650111</v>
+        <v>-0.7094381204235447</v>
       </c>
       <c r="K15">
-        <v>1.50669828788041</v>
+        <v>1.491530965465752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1415,28 +1415,213 @@
         <v>14</v>
       </c>
       <c r="D16">
+        <v>0.4302601096673905</v>
+      </c>
+      <c r="E16">
+        <v>0.07712537718144957</v>
+      </c>
+      <c r="F16">
+        <v>0.7833948421533314</v>
+      </c>
+      <c r="G16">
+        <v>0.02070076115083226</v>
+      </c>
+      <c r="H16">
+        <v>0.3432080428674738</v>
+      </c>
+      <c r="I16">
+        <v>0.7941338554367682</v>
+      </c>
+      <c r="J16">
+        <v>-0.8878993306723153</v>
+      </c>
+      <c r="K16">
+        <v>1.748419550007096</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>0.3496316514591849</v>
+      </c>
+      <c r="E17">
+        <v>0.04633059596073785</v>
+      </c>
+      <c r="F17">
+        <v>0.6529327069576319</v>
+      </c>
+      <c r="G17">
+        <v>0.02666994778449206</v>
+      </c>
+      <c r="H17">
+        <v>0.2896606256707921</v>
+      </c>
+      <c r="I17">
+        <v>0.7491398262998785</v>
+      </c>
+      <c r="J17">
+        <v>-0.8410091432306488</v>
+      </c>
+      <c r="K17">
+        <v>1.540272446149018</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Main analysis</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>0.3778803831558597</v>
+      </c>
+      <c r="E18">
+        <v>0.0927722121850526</v>
+      </c>
+      <c r="F18">
+        <v>0.6629885541266668</v>
+      </c>
+      <c r="G18">
+        <v>0.01258669033108263</v>
+      </c>
+      <c r="H18">
+        <v>0.2827788554998992</v>
+      </c>
+      <c r="I18">
+        <v>0.8060757025672275</v>
+      </c>
+      <c r="J18">
+        <v>-0.7878796200183311</v>
+      </c>
+      <c r="K18">
+        <v>1.543640386330051</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.7</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lancaster et al. (2005) - n / 3</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>0.3880491126151497</v>
+      </c>
+      <c r="E19">
+        <v>0.09835464888198936</v>
+      </c>
+      <c r="F19">
+        <v>0.67774357634831</v>
+      </c>
+      <c r="G19">
+        <v>0.01183191274568021</v>
+      </c>
+      <c r="H19">
+        <v>0.2592882396367674</v>
+      </c>
+      <c r="I19">
+        <v>0.8023464237891476</v>
+      </c>
+      <c r="J19">
+        <v>-0.730600062650111</v>
+      </c>
+      <c r="K19">
+        <v>1.50669828788041</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20">
         <v>0.4282278979822219</v>
       </c>
-      <c r="E16">
+      <c r="E20">
         <v>0.08113238397567168</v>
       </c>
-      <c r="F16">
+      <c r="F20">
         <v>0.7753234119887722</v>
       </c>
-      <c r="G16">
+      <c r="G20">
         <v>0.01943572682182727</v>
       </c>
-      <c r="H16">
+      <c r="H20">
         <v>0.3411699645297598</v>
       </c>
-      <c r="I16">
+      <c r="I20">
         <v>0.837718276238264</v>
       </c>
-      <c r="J16">
+      <c r="J20">
         <v>-0.8840314709338891</v>
       </c>
-      <c r="K16">
+      <c r="K20">
         <v>1.740487266898333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>0.348836077929101</v>
+      </c>
+      <c r="E21">
+        <v>0.05035455311023229</v>
+      </c>
+      <c r="F21">
+        <v>0.6473176027479698</v>
+      </c>
+      <c r="G21">
+        <v>0.02494334252010748</v>
+      </c>
+      <c r="H21">
+        <v>0.290978556479242</v>
+      </c>
+      <c r="I21">
+        <v>0.8020726403474473</v>
+      </c>
+      <c r="J21">
+        <v>-0.8424499707724586</v>
+      </c>
+      <c r="K21">
+        <v>1.540122126630661</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/Th2_pre_post_results.xlsx
+++ b/downloads/Th2_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -883,6 +883,46 @@
           <t>pi_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eg_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eg_df</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>eg_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tf_k0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tf_side</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tf_g</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tf_lo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tf_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -920,6 +960,32 @@
       <c r="K2">
         <v>1.491010096147245</v>
       </c>
+      <c r="L2">
+        <v>1.18145570040356</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>0.2558149862916398</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>0.3754770625085614</v>
+      </c>
+      <c r="R2">
+        <v>0.08562113703531771</v>
+      </c>
+      <c r="S2">
+        <v>0.6653329879818052</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -957,6 +1023,32 @@
       <c r="K3">
         <v>1.382416277346201</v>
       </c>
+      <c r="L3">
+        <v>0.7881006762991539</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>0.4429148916653536</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>0.3875677859925104</v>
+      </c>
+      <c r="R3">
+        <v>0.110162160378363</v>
+      </c>
+      <c r="S3">
+        <v>0.6649734116066579</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -994,6 +1086,32 @@
       <c r="K4">
         <v>1.714655353911577</v>
       </c>
+      <c r="L4">
+        <v>1.448429330643273</v>
+      </c>
+      <c r="M4">
+        <v>12</v>
+      </c>
+      <c r="N4">
+        <v>0.1731183544683136</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q4">
+        <v>0.4253583421227697</v>
+      </c>
+      <c r="R4">
+        <v>0.07956061305328449</v>
+      </c>
+      <c r="S4">
+        <v>0.7711560711922549</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -1031,6 +1149,32 @@
       <c r="K5">
         <v>1.488091743701796</v>
       </c>
+      <c r="L5">
+        <v>1.155374622976278</v>
+      </c>
+      <c r="M5">
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <v>0.2672757568403796</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q5">
+        <v>0.343790229917624</v>
+      </c>
+      <c r="R5">
+        <v>0.0408020555188931</v>
+      </c>
+      <c r="S5">
+        <v>0.6467784043163549</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1068,6 +1212,32 @@
       <c r="K6">
         <v>1.514322770303484</v>
       </c>
+      <c r="L6">
+        <v>1.177604176780871</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <v>0.2573014854656302</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>0.3776102258227688</v>
+      </c>
+      <c r="R6">
+        <v>0.08979736170263097</v>
+      </c>
+      <c r="S6">
+        <v>0.6654230899429066</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1105,6 +1275,32 @@
       <c r="K7">
         <v>1.426522635344288</v>
       </c>
+      <c r="L7">
+        <v>0.7843520853933981</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>0.4450443446418209</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q7">
+        <v>0.3899521832239538</v>
+      </c>
+      <c r="R7">
+        <v>0.1118449746099532</v>
+      </c>
+      <c r="S7">
+        <v>0.6680593918379545</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1142,6 +1338,32 @@
       <c r="K8">
         <v>1.732030371111427</v>
       </c>
+      <c r="L8">
+        <v>1.449466252785263</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>0.172834227237214</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q8">
+        <v>0.4279270937444796</v>
+      </c>
+      <c r="R8">
+        <v>0.08479866525713409</v>
+      </c>
+      <c r="S8">
+        <v>0.7710555222318251</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1179,6 +1401,32 @@
       <c r="K9">
         <v>1.51125861347767</v>
       </c>
+      <c r="L9">
+        <v>1.152147869262168</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>0.2685554440995634</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q9">
+        <v>0.346417333644267</v>
+      </c>
+      <c r="R9">
+        <v>0.04562025828120969</v>
+      </c>
+      <c r="S9">
+        <v>0.6472144090073242</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1216,6 +1464,32 @@
       <c r="K10">
         <v>1.532584955299279</v>
       </c>
+      <c r="L10">
+        <v>1.171827517253328</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>0.2595433644975781</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q10">
+        <v>0.3791406439477505</v>
+      </c>
+      <c r="R10">
+        <v>0.09425489983049373</v>
+      </c>
+      <c r="S10">
+        <v>0.6640263880650072</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1253,6 +1527,32 @@
       <c r="K11">
         <v>1.463528934011129</v>
       </c>
+      <c r="L11">
+        <v>0.7790413043329621</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>0.4480722243204002</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q11">
+        <v>0.3913024394546836</v>
+      </c>
+      <c r="R11">
+        <v>0.1136632069427232</v>
+      </c>
+      <c r="S11">
+        <v>0.6689416719666439</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1290,6 +1590,32 @@
       <c r="K12">
         <v>1.74409665289644</v>
       </c>
+      <c r="L12">
+        <v>1.449889099991215</v>
+      </c>
+      <c r="M12">
+        <v>12</v>
+      </c>
+      <c r="N12">
+        <v>0.1727184757437738</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q12">
+        <v>0.4297566568787799</v>
+      </c>
+      <c r="R12">
+        <v>0.09033114114783442</v>
+      </c>
+      <c r="S12">
+        <v>0.7691821726097254</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1327,6 +1653,32 @@
       <c r="K13">
         <v>1.529354403062184</v>
       </c>
+      <c r="L13">
+        <v>1.14729041433775</v>
+      </c>
+      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <v>0.2704906433162429</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q13">
+        <v>0.3485159356200326</v>
+      </c>
+      <c r="R13">
+        <v>0.05084593920392144</v>
+      </c>
+      <c r="S13">
+        <v>0.6461859320361437</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1364,6 +1716,32 @@
       <c r="K14">
         <v>1.543682394769942</v>
       </c>
+      <c r="L14">
+        <v>1.162934599284073</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="N14">
+        <v>0.2630237375036331</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q14">
+        <v>0.3795726879861506</v>
+      </c>
+      <c r="R14">
+        <v>0.09887826358625079</v>
+      </c>
+      <c r="S14">
+        <v>0.6602671123860504</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1401,6 +1779,32 @@
       <c r="K15">
         <v>1.491530965465752</v>
       </c>
+      <c r="L15">
+        <v>0.7712897926946158</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>0.4525147521220845</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q15">
+        <v>0.3910464225211036</v>
+      </c>
+      <c r="R15">
+        <v>0.1154302675321436</v>
+      </c>
+      <c r="S15">
+        <v>0.6666625775100636</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1438,6 +1842,32 @@
       <c r="K16">
         <v>1.748419550007096</v>
       </c>
+      <c r="L16">
+        <v>1.449105963722643</v>
+      </c>
+      <c r="M16">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>0.1729329054924606</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q16">
+        <v>0.4302601096673908</v>
+      </c>
+      <c r="R16">
+        <v>0.09602496678248168</v>
+      </c>
+      <c r="S16">
+        <v>0.7644952525522999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1475,6 +1905,32 @@
       <c r="K17">
         <v>1.540272446149018</v>
       </c>
+      <c r="L17">
+        <v>1.139855417889576</v>
+      </c>
+      <c r="M17">
+        <v>14</v>
+      </c>
+      <c r="N17">
+        <v>0.2734732480945676</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q17">
+        <v>0.3496316514591849</v>
+      </c>
+      <c r="R17">
+        <v>0.05642084620492105</v>
+      </c>
+      <c r="S17">
+        <v>0.6428424567134488</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1512,6 +1968,32 @@
       <c r="K18">
         <v>1.543640386330051</v>
       </c>
+      <c r="L18">
+        <v>1.148923325716997</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>0.268579122385359</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q18">
+        <v>0.3778803831558598</v>
+      </c>
+      <c r="R18">
+        <v>0.1033199506219045</v>
+      </c>
+      <c r="S18">
+        <v>0.6524408156898152</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1549,6 +2031,32 @@
       <c r="K19">
         <v>1.50669828788041</v>
       </c>
+      <c r="L19">
+        <v>0.7596971259113365</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>0.4592096938637859</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q19">
+        <v>0.3880491126151495</v>
+      </c>
+      <c r="R19">
+        <v>0.1167043035034703</v>
+      </c>
+      <c r="S19">
+        <v>0.6593939217268288</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1586,6 +2094,32 @@
       <c r="K20">
         <v>1.740487266898333</v>
       </c>
+      <c r="L20">
+        <v>1.446129494321108</v>
+      </c>
+      <c r="M20">
+        <v>12</v>
+      </c>
+      <c r="N20">
+        <v>0.1737499387731558</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q20">
+        <v>0.4282278979822217</v>
+      </c>
+      <c r="R20">
+        <v>0.1014734778576495</v>
+      </c>
+      <c r="S20">
+        <v>0.7549823181067938</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1622,6 +2156,32 @@
       </c>
       <c r="K21">
         <v>1.540122126630661</v>
+      </c>
+      <c r="L21">
+        <v>1.12841807728392</v>
+      </c>
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21">
+        <v>0.2781100340777518</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q21">
+        <v>0.3488360779291011</v>
+      </c>
+      <c r="R21">
+        <v>0.06211428608751568</v>
+      </c>
+      <c r="S21">
+        <v>0.6355578697706865</v>
       </c>
     </row>
   </sheetData>
